--- a/artfynd/A 14717-2020 artfynd.xlsx
+++ b/artfynd/A 14717-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14717-2020 artfynd.xlsx
+++ b/artfynd/A 14717-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3527,6 +3527,114 @@
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>118067451</v>
+      </c>
+      <c r="B27" t="n">
+        <v>43019</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>102409</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Högnordisk höfjäril</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Colias hecla</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Lefèbvre, 1836</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Arvnäs, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>694363</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7166030</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Monika Berg</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Monika Berg</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14717-2020 artfynd.xlsx
+++ b/artfynd/A 14717-2020 artfynd.xlsx
@@ -3085,10 +3085,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117640743</v>
+        <v>117637523</v>
       </c>
       <c r="B23" t="n">
-        <v>56751</v>
+        <v>57963</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3097,39 +3097,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102961</v>
+        <v>103044</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3199,10 +3191,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117637523</v>
+        <v>117640743</v>
       </c>
       <c r="B24" t="n">
-        <v>57963</v>
+        <v>56751</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3211,31 +3203,39 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103044</v>
+        <v>102961</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>

--- a/artfynd/A 14717-2020 artfynd.xlsx
+++ b/artfynd/A 14717-2020 artfynd.xlsx
@@ -3085,10 +3085,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117637523</v>
+        <v>117637460</v>
       </c>
       <c r="B23" t="n">
-        <v>57963</v>
+        <v>57769</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3097,31 +3097,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103044</v>
+        <v>103018</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3194,7 +3198,7 @@
         <v>117640743</v>
       </c>
       <c r="B24" t="n">
-        <v>56751</v>
+        <v>56752</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3305,10 +3309,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117637460</v>
+        <v>117637523</v>
       </c>
       <c r="B25" t="n">
-        <v>57768</v>
+        <v>57964</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3317,35 +3321,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103018</v>
+        <v>103044</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>117859361</v>
       </c>
       <c r="B26" t="n">
-        <v>57620</v>
+        <v>57621</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 14717-2020 artfynd.xlsx
+++ b/artfynd/A 14717-2020 artfynd.xlsx
@@ -3752,11 +3752,11 @@
         <v>119113712</v>
       </c>
       <c r="B29" t="n">
-        <v>57314</v>
+        <v>57484</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">

--- a/artfynd/A 14717-2020 artfynd.xlsx
+++ b/artfynd/A 14717-2020 artfynd.xlsx
@@ -3752,7 +3752,7 @@
         <v>119113712</v>
       </c>
       <c r="B29" t="n">
-        <v>57484</v>
+        <v>57487</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>

--- a/artfynd/A 14717-2020 artfynd.xlsx
+++ b/artfynd/A 14717-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1981,10 +1981,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112292314</v>
+        <v>112281199</v>
       </c>
       <c r="B13" t="n">
-        <v>56477</v>
+        <v>57134</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>103057</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sävsparv</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Emberiza schoeniclus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2014,18 +2014,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2063,12 +2055,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-09-15</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-09-15</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2095,10 +2087,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112281199</v>
+        <v>112281210</v>
       </c>
       <c r="B14" t="n">
-        <v>57134</v>
+        <v>57107</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2107,20 +2099,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103057</v>
+        <v>103053</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Lappsparv</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Calcarius lapponicus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2128,10 +2120,18 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2201,10 +2201,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112281233</v>
+        <v>112279516</v>
       </c>
       <c r="B15" t="n">
-        <v>57073</v>
+        <v>56352</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2213,20 +2213,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103042</v>
+        <v>100001</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2234,7 +2234,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
@@ -2311,10 +2315,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112281210</v>
+        <v>112279532</v>
       </c>
       <c r="B16" t="n">
-        <v>57107</v>
+        <v>56507</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2323,25 +2327,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103053</v>
+        <v>102611</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lappsparv</t>
+          <t>Stenfalk</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Calcarius lapponicus</t>
+          <t>Falco columbarius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2351,11 +2355,7 @@
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2425,10 +2425,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112279542</v>
+        <v>112279505</v>
       </c>
       <c r="B17" t="n">
-        <v>56872</v>
+        <v>55525</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2437,31 +2437,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103001</v>
+        <v>100045</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2531,10 +2539,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112279516</v>
+        <v>117637523</v>
       </c>
       <c r="B18" t="n">
-        <v>56352</v>
+        <v>57964</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2543,20 +2551,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100001</v>
+        <v>103044</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2564,18 +2572,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2613,12 +2613,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2645,10 +2645,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112279532</v>
+        <v>117859361</v>
       </c>
       <c r="B19" t="n">
-        <v>56507</v>
+        <v>57623</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2661,21 +2661,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102611</v>
+        <v>103008</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stenfalk</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Falco columbarius</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2685,7 +2685,11 @@
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2723,12 +2727,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2755,10 +2759,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112279543</v>
+        <v>118067451</v>
       </c>
       <c r="B20" t="n">
-        <v>56878</v>
+        <v>43021</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2771,24 +2775,25 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102999</v>
+        <v>102409</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Högnordisk höfjäril</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Colias hecla</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Lefèbvre, 1836</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
@@ -2829,12 +2834,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2843,6 +2848,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2861,10 +2867,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112279505</v>
+        <v>118216602</v>
       </c>
       <c r="B21" t="n">
-        <v>55525</v>
+        <v>56251</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2877,35 +2883,32 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100045</v>
+        <v>208255</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2943,12 +2946,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2957,6 +2960,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2975,14 +2979,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112281154</v>
+        <v>119113712</v>
       </c>
       <c r="B22" t="n">
-        <v>56606</v>
+        <v>57487</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2991,29 +2995,33 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3053,12 +3061,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rörde sig runt stugan under en timme.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3085,10 +3098,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117640743</v>
+        <v>119433044</v>
       </c>
       <c r="B23" t="n">
-        <v>56752</v>
+        <v>57679</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3097,25 +3110,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102961</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3125,11 +3138,7 @@
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3167,12 +3176,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3196,785 +3205,6 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>117637460</v>
-      </c>
-      <c r="B24" t="n">
-        <v>57769</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>103018</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Svartvit flugsnappare</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Ficedula hypoleuca</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Arvnäs, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q24" t="n">
-        <v>694363</v>
-      </c>
-      <c r="R24" t="n">
-        <v>7166030</v>
-      </c>
-      <c r="S24" t="n">
-        <v>10</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>2024-06-08</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>2024-06-08</t>
-        </is>
-      </c>
-      <c r="AD24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>Monika Berg</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>Monika Berg</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>117637523</v>
-      </c>
-      <c r="B25" t="n">
-        <v>57964</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>103044</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Grönsiska</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Spinus spinus</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Arvnäs, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q25" t="n">
-        <v>694363</v>
-      </c>
-      <c r="R25" t="n">
-        <v>7166030</v>
-      </c>
-      <c r="S25" t="n">
-        <v>10</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2024-06-08</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>2024-06-08</t>
-        </is>
-      </c>
-      <c r="AD25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>Monika Berg</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>Monika Berg</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>117859361</v>
-      </c>
-      <c r="B26" t="n">
-        <v>57623</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>103008</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Ärtsångare</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Curruca curruca</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Arvnäs, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q26" t="n">
-        <v>694363</v>
-      </c>
-      <c r="R26" t="n">
-        <v>7166030</v>
-      </c>
-      <c r="S26" t="n">
-        <v>10</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>2024-06-18</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>2024-06-18</t>
-        </is>
-      </c>
-      <c r="AD26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr">
-        <is>
-          <t>Monika Berg</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>Monika Berg</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>118067451</v>
-      </c>
-      <c r="B27" t="n">
-        <v>43021</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>102409</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Högnordisk höfjäril</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Colias hecla</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Lefèbvre, 1836</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Arvnäs, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q27" t="n">
-        <v>694363</v>
-      </c>
-      <c r="R27" t="n">
-        <v>7166030</v>
-      </c>
-      <c r="S27" t="n">
-        <v>10</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>2024-06-27</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>2024-06-27</t>
-        </is>
-      </c>
-      <c r="AD27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="inlineStr"/>
-      <c r="AG27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr">
-        <is>
-          <t>Monika Berg</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>Monika Berg</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>118216602</v>
-      </c>
-      <c r="B28" t="n">
-        <v>56251</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>208255</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Skogsödla</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Zootoca vivipara</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Jacquin, 1787)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Arvnäs, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q28" t="n">
-        <v>694363</v>
-      </c>
-      <c r="R28" t="n">
-        <v>7166030</v>
-      </c>
-      <c r="S28" t="n">
-        <v>10</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>2024-07-03</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>2024-07-03</t>
-        </is>
-      </c>
-      <c r="AD28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="inlineStr"/>
-      <c r="AG28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="inlineStr"/>
-      <c r="AW28" t="inlineStr">
-        <is>
-          <t>Monika Berg</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>Monika Berg</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>119113712</v>
-      </c>
-      <c r="B29" t="n">
-        <v>57487</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>100048</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Mindre hackspett</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Dryobates minor</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Arvnäs, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q29" t="n">
-        <v>694363</v>
-      </c>
-      <c r="R29" t="n">
-        <v>7166030</v>
-      </c>
-      <c r="S29" t="n">
-        <v>10</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rörde sig runt stugan under en timme.</t>
-        </is>
-      </c>
-      <c r="AD29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="inlineStr"/>
-      <c r="AW29" t="inlineStr">
-        <is>
-          <t>Monika Berg</t>
-        </is>
-      </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>Monika Berg</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>119433044</v>
-      </c>
-      <c r="B30" t="n">
-        <v>57679</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>103015</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Regulus regulus</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Arvnäs, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q30" t="n">
-        <v>694363</v>
-      </c>
-      <c r="R30" t="n">
-        <v>7166030</v>
-      </c>
-      <c r="S30" t="n">
-        <v>10</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AD30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>Monika Berg</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>Monika Berg</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
